--- a/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,39 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>VBSKA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>`Gynekologisk och postpartumvård, verksamhetsförlagd utbildning` → `VÅ3086` (nedlagd 2017-04-07) — plain-text-referens; rad: - Gynekologisk och postpartumvård, verksamhetsförlagd utbildning, 9 hp</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VBSKA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -496,11 +496,40 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>VSSKG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` → `VÅ1061` (nedlagd 2025-06-03) — plain-text-referens; rad: - Introduktion omvårdnad och etik - Huvudområde Omvårdnad, 15 hp</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Gynekologisk och postpartumvård, verksamhetsförlagd utbildning` → `VÅ3086` (nedlagd 2017-04-07) — plain-text-referens; rad: - Gynekologisk och postpartumvård, verksamhetsförlagd utbildning, 9 hp</t>
+          <t>`Gynekologisk och postpartumvård, verksamhetsförlagd utbildning` → `VÅ3086` (nedlagd 2017-04-07) — plain-text-referens</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` → `VÅ1061` (nedlagd 2025-06-03) — plain-text-referens; rad: - Introduktion omvårdnad och etik - Huvudområde Omvårdnad, 15 hp</t>
+          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` → `VÅ1061` (nedlagd 2025-06-03) — plain-text-referens</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">

--- a/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2019-09-10</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>`Gynekologisk och postpartumvård, verksamhetsförlagd utbildning` → `VÅ3086` (nedlagd 2017-04-07) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VBSKA</t>
         </is>
@@ -509,27 +527,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` → `VÅ1061` (nedlagd 2025-06-03) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -508,7 +514,12 @@
           <t>`Gynekologisk och postpartumvård, verksamhetsförlagd utbildning` → `VÅ3086` (nedlagd 2017-04-07) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`VÅ3086` (nedlagd 2017-04-07) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VBSKA</t>
         </is>
@@ -545,19 +556,24 @@
           <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` → `VÅ1061` (nedlagd 2025-06-03) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`VÅ1061` (nedlagd 2025-06-03) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:H3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Gynekologisk och postpartumvård, verksamhetsförlagd utbildning` → `VÅ3086` (nedlagd 2017-04-07) — plain-text-referens</t>
+          <t>`Gynekologisk och postpartumvård, verksamhetsförlagd utbildning`</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad` → `VÅ1061` (nedlagd 2025-06-03) — plain-text-referens</t>
+          <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">

--- a/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -528,52 +528,224 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>VSJPG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>`Metoder för evidensbaserad vård II`</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`GVÅ2ZY` (nedlagd 2026-09-04) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSJPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>VSSKG</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Utbildningsplan</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2018-12-04</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2020-12-17</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>`Introduktion omvårdnad och etik - Huvudområde Omvårdnad`</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>`VÅ1061` (nedlagd 2025-06-03) — plain-text-referens</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>VSSKG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>`Människans grundläggande omvårdnadsbehov - Huvudområde Omvårdnad`</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`GVÅ2RA` (nedlagd 2026-09-04) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>VSSKG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>`Metoder för evidensbaserad vård II - Huvudområde Omvårdnad`</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`GVÅ2ZY` (nedlagd 2026-09-04) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>VSSKG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Programmet listar nedlagd kurs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>`Personcentrerad vård med fördjupning inom omvårdnad - Huvudområde Omvårdnad`</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>`GVÅ2ZG` (nedlagd 2026-09-04) — wikilink-länk till nedlagd kod</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=VSSKG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
